--- a/internal_doc/05.测试设计/story/内置SQL/Story-内置SQL中增加指定index的hint.xlsx
+++ b/internal_doc/05.测试设计/story/内置SQL/Story-内置SQL中增加指定index的hint.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>name</t>
   </si>
@@ -49,14 +49,6 @@
   </si>
   <si>
     <t>execution_type2</t>
-  </si>
-  <si>
-    <t>如：/*+use_index(myindex)*/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如：/*+use_hash()*/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>如：/*+use_index(t1, myindex)*/</t>
@@ -362,10 +354,6 @@
       <t xml:space="preserve">
 2、检查记录返回结果</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询失败，返回结果提示参数错误，提示信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -580,10 +568,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>查询失败，返回结果提示集合不存在，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hint格式错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -644,6 +628,231 @@
   </si>
   <si>
     <t>属于同一个SELECT语句的hint使用空格分隔。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、查询后返回的结果正确
+2、查询时该集合不走指定索引（如：
+查询前"TotalIndexRead": 106，
+查询后"TotalIndexRead": 106）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint的格式为"/*+hint1 hint2 ...*/"。但我们希望控制某个SELECT语句时，只需要在这个SELECT语句结尾处增加hint即可。属于同一个SELECT语句的hint使用空格分隔。
+说明：hint如果不生效或者格式不对，select查询成功，但不走hint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+hint的格式为"/*+hint1 hint2 ...*/"。但我们希望控制某个SELECT语句时，只需要在这个SELECT语句结尾处增加hint即可。属于同一个SELECT语句的hint使用空格分隔。
+说明：hint如果不生效或者格式不对，select查询成功，但不走hint
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint指定的表和索引跟select语句中表名不对应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，且指定的索引不存在，如：
+SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, myindex)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、查询后返回的结果正确
+2、hint格式或参数错误时，select查询成功，但不走hint，即不报错亦不走索引扫描（如：
+查询前"TotalIndexRead": 106，
+查询后"TotalIndexRead": 109）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL为嵌套查询，且在嵌套查询中的不同SELECT语句中使用hint，如：
+select * from (((( t1 inner join t2 on t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t1, aa)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ) 
+  inner join as t3 on t2.b = t3.c </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t2, bb)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )
+    inner join as t4 on t3.c = t4.d </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/*+use_index(t3, cc)*/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+      inner join as t5 on t4.d = t5.e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t4, dd)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )
+        inner join as t6 on t5.e = t6.f 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t5, ee) use_index(t6, ff)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、查询后返回的结果正确
+2、查询时hint对应的集合有走指定索引（如：
+查询前"TotalIndexRead": 106，
+查询后"TotalIndexRead": 112）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select关联多个表指定多个hint查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -822,8 +1031,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I12" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I14" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I14"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1142,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -1184,15 +1393,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="40.5">
+    <row r="2" spans="1:9" ht="108">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -1209,15 +1418,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="94.5">
+    <row r="3" spans="1:9" ht="135">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -1229,10 +1438,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -1240,13 +1449,13 @@
     </row>
     <row r="4" spans="1:9" ht="108">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1258,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -1269,13 +1478,13 @@
     </row>
     <row r="5" spans="1:9" ht="108">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1287,10 +1496,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -1298,13 +1507,13 @@
     </row>
     <row r="6" spans="1:9" ht="135">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -1316,10 +1525,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -1327,13 +1536,13 @@
     </row>
     <row r="7" spans="1:9" ht="229.5">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -1345,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -1356,13 +1565,13 @@
     </row>
     <row r="8" spans="1:9" ht="94.5">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1374,10 +1583,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -1385,13 +1594,13 @@
     </row>
     <row r="9" spans="1:9" ht="94.5">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -1403,10 +1612,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -1414,10 +1623,10 @@
     </row>
     <row r="10" spans="1:9" ht="121.5">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1429,22 +1638,18 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="67.5">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="1" t="s">
-        <v>43</v>
+    <row r="11" spans="1:9" ht="108">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1456,24 +1661,20 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:9" ht="135">
+    <row r="12" spans="1:9" ht="94.5">
       <c r="A12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>48</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -1485,24 +1686,69 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+    <row r="13" spans="1:9" ht="135">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+    <row r="14" spans="1:9" ht="216">
+      <c r="A14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="5"/>
@@ -1519,16 +1765,6 @@
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/内置SQL/Story-内置SQL中增加指定index的hint.xlsx
+++ b/internal_doc/05.测试设计/story/内置SQL/Story-内置SQL中增加指定index的hint.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>name</t>
   </si>
@@ -56,10 +56,6 @@
   </si>
   <si>
     <t>如：/*+use_index(t1, myindex1) use_index(t2, myindex2) use_hash()*/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在嵌套查询中的不同SELECT语句中使用hint</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -80,22 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指定关联方式为use_hash关联</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定当前集合使用索引扫描</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定某个集合使用索引扫描</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在一个SELECT语句中使用多个hint指定多个集合使用索引扫描</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>如：/*+use_index(NULL)*/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -151,37 +131,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>/*+use_index(t1, myindex)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL的一个SELECT语句中使用多个hint指定多个集合使用索引扫描，如：
-SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t1, myindex1) use_index(t2, myindex2) use_hash()*/</t>
     </r>
     <r>
       <rPr>
@@ -250,18 +199,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>select查询多个表中字段，指定hint为/*+use_index(myindex)*/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定当前集合不使用索引（该集合查询的字段有创建索引）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个select中多个hint重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">如：SELECT </t>
     </r>
@@ -361,14 +298,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hint指定的索引不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>select指定集合使用索引扫描，集合不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">如：……t4.c  </t>
     </r>
@@ -411,7 +340,538 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL为嵌套查询，且在嵌套查询中的不同SELECT语句中使用hint，如：
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，如：
+SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t1, myindex) use_index(t1, myindex)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，且指定的索引不存在，如（myindex索引不存在）：
+SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t1, myindex)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，select指定集合使用索引扫描，集合不存在，如：
+SELECT * FROM foo.bar WHERE a = 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(myindex)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属于同一个SELECT语句的hint使用空格分隔。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、查询后返回的结果正确
+2、查询时该集合不走指定索引（如：
+查询前"TotalIndexRead": 106，
+查询后"TotalIndexRead": 106）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+hint的格式为"/*+hint1 hint2 ...*/"。但我们希望控制某个SELECT语句时，只需要在这个SELECT语句结尾处增加hint即可。属于同一个SELECT语句的hint使用空格分隔。
+说明：hint如果不生效或者格式不对，select查询成功，但不走hint
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，且指定的索引不存在，如：
+SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, myindex)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、查询后返回的结果正确
+2、hint格式或参数错误时，select查询成功，但不走hint，即不报错亦不走索引扫描（如：
+查询前"TotalIndexRead": 106，
+查询后"TotalIndexRead": 109）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、查询后返回的结果正确
+2、查询时hint对应的集合有走指定索引（如：
+查询前"TotalIndexRead": 106，
+查询后"TotalIndexRead": 112）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如：/*+use_index(myindex)*/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，如：
+  SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b /*+use_index(t1, myindex)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> use_index(t1, myindex)*/
+或
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>use_index(t1, myindex)*/
+或
+  /*+use_index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">     --为空
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  hint在select前面或中间位置,如：SELECT /*+use_index(t1, myindex) t1.a FROM foo.bar1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖left join/right join/inner join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sql语句关键字：
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL覆盖如下语句关键字，并指定使用索引扫描，sql语句关键字：
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL为嵌套查询，且在嵌套查询中的不同SELECT语句中使用索引扫描，如：
+select * from (((( t1 inner join t2 on t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t1, aa)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ) 
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>left join</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as t3 on t2.b = t3.c </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t2, bb)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>right join</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as t4 on t3.c = t4.d </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/*+use_index(t3, cc)*/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+      inner join as t5 on t4.d = t5.e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t4, dd)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )
+        inner join as t6 on t5.e = t6.f 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t5, ee) use_index(t6, ff)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL的一个SELECT语句中使用多个hint指定多个集合使用索引扫描，如：
+SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(t1, myindex1) use_index(t2, myindex2) use_hash()*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL为嵌套查询，且在嵌套查询中的不同SELECT语句中使用hint指定使用索引扫描，如：
 SELECT t1.a, t2.b, t2.cnt
   FROM foo.bar1 AS t1
     INNER JOIN (
@@ -471,388 +931,76 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，如：
-SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t1, myindex) use_index(t1, myindex)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查记录返回结果</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，且指定的索引不存在，如（myindex索引不存在）：
-SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t1, myindex)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>1、进入sdb，使用db.exec()执行内置SQL语句，验证原有内置SQL功能是否正常可用，如：
 2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdb运行正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，select指定集合使用索引扫描，集合不存在，如：
-SELECT * FROM foo.bar WHERE a = 1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(myindex)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查记录返回结果</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hint格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，如：
-SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b /*+use_index(t1, myindex)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> use_index(t1, myindex)*/
-或
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>use_index(t1, myindex) use_index(t1, myindex)*/
-2、检查记录返回结果</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属于同一个SELECT语句的hint使用空格分隔。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、查询后返回的结果正确
-2、查询时该集合不走指定索引（如：
-查询前"TotalIndexRead": 106，
-查询后"TotalIndexRead": 106）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hint的格式为"/*+hint1 hint2 ...*/"。但我们希望控制某个SELECT语句时，只需要在这个SELECT语句结尾处增加hint即可。属于同一个SELECT语句的hint使用空格分隔。
-说明：hint如果不生效或者格式不对，select查询成功，但不走hint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-hint的格式为"/*+hint1 hint2 ...*/"。但我们希望控制某个SELECT语句时，只需要在这个SELECT语句结尾处增加hint即可。属于同一个SELECT语句的hint使用空格分隔。
-说明：hint如果不生效或者格式不对，select查询成功，但不走hint
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hint指定的表和索引跟select语句中表名不对应</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定某个集合使用索引扫描，且指定的索引不存在，如：
-SELECT t1.a, t2.b FROM foo.bar1 AS t1 INNER JOIN foo.bar2 AS t2 ON t1.a = t2.b </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>t3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, myindex)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、查询后返回的结果正确
-2、hint格式或参数错误时，select查询成功，但不走hint，即不报错亦不走索引扫描（如：
-查询前"TotalIndexRead": 106，
-查询后"TotalIndexRead": 109）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL为嵌套查询，且在嵌套查询中的不同SELECT语句中使用hint，如：
-select * from (((( t1 inner join t2 on t1.a = t2.b </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t1, aa)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ) 
-  inner join as t3 on t2.b = t3.c </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t2, bb)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> )
-    inner join as t4 on t3.c = t4.d </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">/*+use_index(t3, cc)*/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">)
-      inner join as t5 on t4.d = t5.e </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t4, dd)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> )
-        inner join as t6 on t5.e = t6.f 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(t5, ee) use_index(t6, ff)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、查询后返回的结果正确
-2、查询时hint对应的集合有走指定索引（如：
-查询前"TotalIndexRead": 106，
-查询后"TotalIndexRead": 112）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>select关联多个表指定多个hint查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原有内置SQL功能正常可用，执行SQL后查询结果合理正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽测原有基本功能，检查新增hint后对原有功能是否有影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定关联方式为use_hash关联_st.sql.hint.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定当前集合使用索引扫描_st.sql.hint.002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定当前集合不使用索引（该集合查询的字段有创建索引）_st.sql.hint.003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定某个集合使用索引扫描_st.sql.hint.004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在一个SELECT语句中使用多个hint指定多个集合使用索引扫描_st.sql.hint.005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在嵌套查询中的不同SELECT语句中使用hint_st.sql.hint.006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select查询多个表中字段，指定hint为/*+use_index(myindex)*/_st.sql.hint.007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个select中多个hint重复_st.sql.hint.008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint指定的索引不存在_st.sql.hint.009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint指定的表和索引跟select语句中表名不对应_st.sql.hint.010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select指定集合使用索引扫描，集合不存在_st.sql.hint.011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint格式错误_st.sql.hint.012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select关联多个表指定多个hint查询_st.sql.hint.013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select覆盖语句关键字并指定hint_st.sql.hint.014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原有内置SQL功能验证（新增hint对原有SQL不影响）_st.sql.hint.015</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -922,7 +1070,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -940,6 +1088,12 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1031,8 +1185,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I14" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I16" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I16"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1351,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -1393,15 +1547,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="108">
+    <row r="2" spans="1:9" ht="40.5">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -1420,28 +1574,28 @@
     </row>
     <row r="3" spans="1:9" ht="135">
       <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -1449,13 +1603,13 @@
     </row>
     <row r="4" spans="1:9" ht="108">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1467,10 +1621,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -1478,13 +1632,13 @@
     </row>
     <row r="5" spans="1:9" ht="108">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1496,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -1507,13 +1661,13 @@
     </row>
     <row r="6" spans="1:9" ht="135">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -1525,10 +1679,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -1536,13 +1690,13 @@
     </row>
     <row r="7" spans="1:9" ht="229.5">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -1554,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -1565,28 +1719,28 @@
     </row>
     <row r="8" spans="1:9" ht="94.5">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -1594,13 +1748,13 @@
     </row>
     <row r="9" spans="1:9" ht="94.5">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -1612,10 +1766,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -1623,10 +1777,10 @@
     </row>
     <row r="10" spans="1:9" ht="121.5">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1638,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -1649,7 +1803,7 @@
     </row>
     <row r="11" spans="1:9" ht="108">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1661,20 +1815,20 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="94.5">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -1686,24 +1840,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="135">
+    <row r="13" spans="1:9" ht="189">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -1715,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3">
         <v>1</v>
@@ -1726,10 +1880,13 @@
     </row>
     <row r="14" spans="1:9" ht="216">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1741,29 +1898,73 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
+    <row r="15" spans="1:9" ht="94.5">
+      <c r="A15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+    <row r="16" spans="1:9" ht="81">
+      <c r="A16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/story/内置SQL/Story-内置SQL中增加指定index的hint.xlsx
+++ b/internal_doc/05.测试设计/story/内置SQL/Story-内置SQL中增加指定index的hint.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
   <si>
     <t>name</t>
   </si>
@@ -82,37 +82,6 @@
   <si>
     <t>1、查询后返回的结果正确
 2、查询时有走指定索引（如：查询前"TotalIndexRead": 106，查询后"TotalIndexRead": 107）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定当前集合使用索引扫描，如：
-SELECT * FROM foo.bar WHERE a = 1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/*+use_index(myindex)*/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1001,6 +970,41 @@
   </si>
   <si>
     <t>原有内置SQL功能验证（新增hint对原有SQL不影响）_st.sql.hint.015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、进入sdb，使用db.exec()执行内置SQL语句，内置SQL指定当前集合使用索引扫描，如：
+SELECT * FROM foo.bar WHERE a = 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/*+use_index(myindex)*/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、检查记录返回结果，并检查查询是否有走指定索引（如：使用sqlTest2工具，或db.snapshot(6)查看"TotalIndexRead"索引读的次数）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1549,10 +1553,10 @@
     </row>
     <row r="2" spans="1:9" ht="40.5">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -1566,18 +1570,22 @@
       <c r="F2" s="3">
         <v>1</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="I2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="135">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
@@ -1592,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>15</v>
@@ -1603,7 +1611,7 @@
     </row>
     <row r="4" spans="1:9" ht="108">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>14</v>
@@ -1621,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -1632,7 +1640,7 @@
     </row>
     <row r="5" spans="1:9" ht="108">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
@@ -1650,10 +1658,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -1661,7 +1669,7 @@
     </row>
     <row r="6" spans="1:9" ht="135">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>10</v>
@@ -1679,10 +1687,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -1690,10 +1698,10 @@
     </row>
     <row r="7" spans="1:9" ht="229.5">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
@@ -1708,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -1719,10 +1727,10 @@
     </row>
     <row r="8" spans="1:9" ht="94.5">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
@@ -1737,10 +1745,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -1748,10 +1756,10 @@
     </row>
     <row r="9" spans="1:9" ht="94.5">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
@@ -1766,10 +1774,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3">
         <v>1</v>
@@ -1777,7 +1785,7 @@
     </row>
     <row r="10" spans="1:9" ht="121.5">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
@@ -1792,10 +1800,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -1803,7 +1811,7 @@
     </row>
     <row r="11" spans="1:9" ht="108">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1815,20 +1823,20 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="94.5">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -1840,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3">
         <v>1</v>
@@ -1851,10 +1859,10 @@
     </row>
     <row r="13" spans="1:9" ht="189">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
@@ -1869,10 +1877,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3">
         <v>1</v>
@@ -1880,10 +1888,10 @@
     </row>
     <row r="14" spans="1:9" ht="216">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>13</v>
@@ -1898,10 +1906,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3">
         <v>1</v>
@@ -1909,10 +1917,10 @@
     </row>
     <row r="15" spans="1:9" ht="94.5">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>13</v>
@@ -1920,19 +1928,19 @@
       <c r="D15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9" ht="81">
       <c r="A16" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
@@ -1947,10 +1955,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="I16" s="3">
         <v>1</v>
